--- a/R_analysis/output/tables/Tabela_ITS_COVID.xlsx
+++ b/R_analysis/output/tables/Tabela_ITS_COVID.xlsx
@@ -422,7 +422,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
     </row>
